--- a/static/equipment_import_template.xlsx
+++ b/static/equipment_import_template.xlsx
@@ -1,54 +1,162 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\dungnt\workspaces\JOB\VPEI\static\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12915"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment_Template" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Equipment_Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+  <si>
+    <t>Mã phân loại</t>
+  </si>
+  <si>
+    <t>Tên thiết bị</t>
+  </si>
+  <si>
+    <t>Số lượng</t>
+  </si>
+  <si>
+    <t>Đơn vị tính</t>
+  </si>
+  <si>
+    <t>Cách tính</t>
+  </si>
+  <si>
+    <t>EF CO2</t>
+  </si>
+  <si>
+    <t>EF CH4</t>
+  </si>
+  <si>
+    <t>EF N2O</t>
+  </si>
+  <si>
+    <t>GWP</t>
+  </si>
+  <si>
+    <t>EF</t>
+  </si>
+  <si>
+    <t>Mô tả</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Lò hơi đốt than</t>
+  </si>
+  <si>
+    <t>Cái</t>
+  </si>
+  <si>
+    <t>Cách tính 1</t>
+  </si>
+  <si>
+    <t>Lò hơi chính nhà xưởng</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Xe nâng chạy dầu</t>
+  </si>
+  <si>
+    <t>Chiếc</t>
+  </si>
+  <si>
+    <t>Xe nâng vận chuyển bến bãi</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Điều hòa trung tâm VRV</t>
+  </si>
+  <si>
+    <t>Hệ thống</t>
+  </si>
+  <si>
+    <t>Cách tính 2</t>
+  </si>
+  <si>
+    <t>Hệ thống điều hòa văn phòng</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Máy phát điện dự phòng</t>
+  </si>
+  <si>
+    <t>Cách tính 3</t>
+  </si>
+  <si>
+    <t>Dự phòng khi mất điện lưới</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Máy xúc đào</t>
+  </si>
+  <si>
+    <t>Cách tính 4</t>
+  </si>
+  <si>
+    <t>Máy xúc công trình</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D1F3C"/>
-        <bgColor rgb="000D1F3C"/>
+        <fgColor rgb="FF0D1F3C"/>
+        <bgColor rgb="FF0D1F3C"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,115 +170,57 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -458,273 +508,192 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="5" width="15" customWidth="1"/>
+    <col min="6" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mã phân loại</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Tên thiết bị</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Số lượng</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Đơn vị tính</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Cách tính</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>EF CO2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>EF CH4</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>EF N2O</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>GWP</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>EF</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Lò hơi đốt than</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Cách tính 1</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Lò hơi chính nhà xưởng</t>
-        </is>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4">
+        <v>100</v>
+      </c>
+      <c r="G2" s="4">
+        <v>100</v>
+      </c>
+      <c r="H2" s="4">
+        <v>100</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Xe nâng chạy dầu</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Chiếc</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cách tính 1</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Xe nâng vận chuyển bến bãi</t>
-        </is>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="4">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4">
+        <v>150</v>
+      </c>
+      <c r="H3" s="4">
+        <v>100</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Điều hòa trung tâm VRV</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Hệ thống</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cách tính 2</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="6" t="n">
-        <v>2088</v>
-      </c>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Hệ thống điều hòa văn phòng</t>
-        </is>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="6">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Máy phát điện dự phòng</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cách tính 3</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="4" t="n">
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="4">
         <v>0.78</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Dự phòng khi mất điện lưới</t>
-        </is>
+      <c r="K5" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Máy xúc đào</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Chiếc</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Cách tính 4</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Máy xúc công trình</t>
-        </is>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
